--- a/Employee_Reports_wi52/Kim Harvey Cuevas Ayag Q0609.xlsx
+++ b/Employee_Reports_wi52/Kim Harvey Cuevas Ayag Q0609.xlsx
@@ -37,7 +37,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -54,12 +54,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00FFC7CE"/>
         <bgColor rgb="00FFC7CE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFACD"/>
-        <bgColor rgb="00FFFACD"/>
       </patternFill>
     </fill>
   </fills>
@@ -81,7 +75,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -93,9 +87,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -463,7 +454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K41"/>
+  <dimension ref="A1:K42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -475,7 +466,7 @@
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="18" customWidth="1" min="8" max="8"/>
     <col width="13" customWidth="1" min="9" max="9"/>
-    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="9" customWidth="1" min="10" max="10"/>
     <col width="9" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
@@ -578,11 +569,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>335</v>
+        <v>327</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -627,11 +618,11 @@
         </is>
       </c>
       <c r="H4" s="3" t="n">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -676,11 +667,11 @@
         </is>
       </c>
       <c r="H5" s="3" t="n">
-        <v>335</v>
+        <v>327</v>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -725,11 +716,11 @@
         </is>
       </c>
       <c r="H6" s="3" t="n">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -774,11 +765,11 @@
         </is>
       </c>
       <c r="H7" s="3" t="n">
-        <v>335</v>
+        <v>327</v>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -823,11 +814,11 @@
         </is>
       </c>
       <c r="H8" s="3" t="n">
-        <v>336</v>
+        <v>328</v>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -872,11 +863,11 @@
         </is>
       </c>
       <c r="H9" s="3" t="n">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -921,11 +912,11 @@
         </is>
       </c>
       <c r="H10" s="3" t="n">
-        <v>336</v>
+        <v>328</v>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -970,11 +961,11 @@
         </is>
       </c>
       <c r="H11" s="3" t="n">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1019,11 +1010,11 @@
         </is>
       </c>
       <c r="H12" s="3" t="n">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -1068,11 +1059,11 @@
         </is>
       </c>
       <c r="H13" s="3" t="n">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -1117,11 +1108,11 @@
         </is>
       </c>
       <c r="H14" s="3" t="n">
-        <v>338</v>
+        <v>330</v>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
@@ -1166,11 +1157,11 @@
         </is>
       </c>
       <c r="H15" s="3" t="n">
-        <v>338</v>
+        <v>330</v>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -1215,11 +1206,11 @@
         </is>
       </c>
       <c r="H16" s="3" t="n">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
@@ -1252,11 +1243,11 @@
         </is>
       </c>
       <c r="H17" s="3" t="n">
-        <v>371</v>
+        <v>363</v>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
@@ -1301,11 +1292,11 @@
         </is>
       </c>
       <c r="H18" s="3" t="n">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
@@ -1350,11 +1341,11 @@
         </is>
       </c>
       <c r="H19" s="3" t="n">
-        <v>338</v>
+        <v>330</v>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
@@ -1387,11 +1378,11 @@
         </is>
       </c>
       <c r="H20" s="3" t="n">
-        <v>338</v>
+        <v>330</v>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
@@ -1436,11 +1427,11 @@
         </is>
       </c>
       <c r="H21" s="3" t="n">
-        <v>349</v>
+        <v>341</v>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
@@ -1485,11 +1476,11 @@
         </is>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-29</v>
+        <v>-37</v>
       </c>
       <c r="I22" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J22" s="4" t="inlineStr">
@@ -1534,11 +1525,11 @@
         </is>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-27</v>
+        <v>-35</v>
       </c>
       <c r="I23" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J23" s="4" t="inlineStr">
@@ -1583,11 +1574,11 @@
         </is>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-28</v>
+        <v>-36</v>
       </c>
       <c r="I24" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J24" s="4" t="inlineStr">
@@ -1632,11 +1623,11 @@
         </is>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-14</v>
+        <v>-22</v>
       </c>
       <c r="I25" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J25" s="4" t="inlineStr">
@@ -1681,11 +1672,11 @@
         </is>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-6</v>
+        <v>-14</v>
       </c>
       <c r="I26" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J26" s="4" t="inlineStr">
@@ -1730,11 +1721,11 @@
         </is>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-7</v>
+        <v>-15</v>
       </c>
       <c r="I27" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J27" s="4" t="inlineStr">
@@ -1779,11 +1770,11 @@
         </is>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-7</v>
+        <v>-15</v>
       </c>
       <c r="I28" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J28" s="4" t="inlineStr">
@@ -1828,11 +1819,11 @@
         </is>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-9</v>
+        <v>-17</v>
       </c>
       <c r="I29" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J29" s="4" t="inlineStr">
@@ -1877,11 +1868,11 @@
         </is>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-3</v>
+        <v>-11</v>
       </c>
       <c r="I30" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J30" s="4" t="inlineStr">
@@ -1914,352 +1905,352 @@
         </is>
       </c>
       <c r="H31" s="4" t="n">
+        <v>-11</v>
+      </c>
+      <c r="I31" s="4" t="inlineStr">
+        <is>
+          <t>27-Aug-2026</t>
+        </is>
+      </c>
+      <c r="J31" s="4" t="inlineStr">
+        <is>
+          <t>EXPIRED</t>
+        </is>
+      </c>
+      <c r="K31" s="4" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>SRM Laser Distance Meter Adjustment (SOPs)</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr"/>
+      <c r="D32" s="4" t="inlineStr"/>
+      <c r="E32" s="4" t="inlineStr"/>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>21-Aug-2025</t>
+        </is>
+      </c>
+      <c r="G32" s="4" t="inlineStr">
+        <is>
+          <t>21-Aug-2026</t>
+        </is>
+      </c>
+      <c r="H32" s="4" t="n">
+        <v>-7</v>
+      </c>
+      <c r="I32" s="4" t="inlineStr">
+        <is>
+          <t>27-Aug-2026</t>
+        </is>
+      </c>
+      <c r="J32" s="4" t="inlineStr">
+        <is>
+          <t>EXPIRED</t>
+        </is>
+      </c>
+      <c r="K32" s="4" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="n">
+        <v>31</v>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>ASI- I  3.0 Profibus Gateway Configurations (SOPs)</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr"/>
+      <c r="D33" s="4" t="inlineStr"/>
+      <c r="E33" s="4" t="inlineStr"/>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>24-Aug-2025</t>
+        </is>
+      </c>
+      <c r="G33" s="4" t="inlineStr">
+        <is>
+          <t>24-Aug-2026</t>
+        </is>
+      </c>
+      <c r="H33" s="4" t="n">
+        <v>-4</v>
+      </c>
+      <c r="I33" s="4" t="inlineStr">
+        <is>
+          <t>27-Aug-2026</t>
+        </is>
+      </c>
+      <c r="J33" s="4" t="inlineStr">
+        <is>
+          <t>EXPIRED</t>
+        </is>
+      </c>
+      <c r="K33" s="4" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>Equipment Request &amp; Handover Procedure(AMH) (SOPs)</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr"/>
+      <c r="D34" s="4" t="inlineStr"/>
+      <c r="E34" s="4" t="inlineStr"/>
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t>24-Aug-2025</t>
+        </is>
+      </c>
+      <c r="G34" s="4" t="inlineStr">
+        <is>
+          <t>24-Aug-2026</t>
+        </is>
+      </c>
+      <c r="H34" s="4" t="n">
+        <v>-4</v>
+      </c>
+      <c r="I34" s="4" t="inlineStr">
+        <is>
+          <t>27-Aug-2026</t>
+        </is>
+      </c>
+      <c r="J34" s="4" t="inlineStr">
+        <is>
+          <t>EXPIRED</t>
+        </is>
+      </c>
+      <c r="K34" s="4" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="n">
+        <v>33</v>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>Storage Retrieval Machine Software Recovery Procedure (SOPs)</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr"/>
+      <c r="D35" s="4" t="inlineStr"/>
+      <c r="E35" s="4" t="inlineStr"/>
+      <c r="F35" s="4" t="inlineStr">
+        <is>
+          <t>25-Aug-2025</t>
+        </is>
+      </c>
+      <c r="G35" s="4" t="inlineStr">
+        <is>
+          <t>25-Aug-2026</t>
+        </is>
+      </c>
+      <c r="H35" s="4" t="n">
         <v>-3</v>
       </c>
-      <c r="I31" s="4" t="inlineStr">
-        <is>
-          <t>19-Aug-2026</t>
-        </is>
-      </c>
-      <c r="J31" s="4" t="inlineStr">
+      <c r="I35" s="4" t="inlineStr">
+        <is>
+          <t>27-Aug-2026</t>
+        </is>
+      </c>
+      <c r="J35" s="4" t="inlineStr">
         <is>
           <t>EXPIRED</t>
         </is>
       </c>
-      <c r="K31" s="4" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="5" t="n">
-        <v>30</v>
-      </c>
-      <c r="B32" s="5" t="inlineStr">
-        <is>
-          <t>SRM Laser Distance Meter Adjustment (SOPs)</t>
-        </is>
-      </c>
-      <c r="C32" s="5" t="inlineStr"/>
-      <c r="D32" s="5" t="inlineStr"/>
-      <c r="E32" s="5" t="inlineStr"/>
-      <c r="F32" s="5" t="inlineStr">
-        <is>
-          <t>21-Aug-2025</t>
-        </is>
-      </c>
-      <c r="G32" s="5" t="inlineStr">
-        <is>
-          <t>21-Aug-2026</t>
-        </is>
-      </c>
-      <c r="H32" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I32" s="5" t="inlineStr">
-        <is>
-          <t>19-Aug-2026</t>
-        </is>
-      </c>
-      <c r="J32" s="5" t="inlineStr">
-        <is>
-          <t>EXPIRING SOON</t>
-        </is>
-      </c>
-      <c r="K32" s="5" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="5" t="n">
-        <v>31</v>
-      </c>
-      <c r="B33" s="5" t="inlineStr">
-        <is>
-          <t>ASI- I  3.0 Profibus Gateway Configurations (SOPs)</t>
-        </is>
-      </c>
-      <c r="C33" s="5" t="inlineStr"/>
-      <c r="D33" s="5" t="inlineStr"/>
-      <c r="E33" s="5" t="inlineStr"/>
-      <c r="F33" s="5" t="inlineStr">
-        <is>
-          <t>24-Aug-2025</t>
-        </is>
-      </c>
-      <c r="G33" s="5" t="inlineStr">
-        <is>
-          <t>24-Aug-2026</t>
-        </is>
-      </c>
-      <c r="H33" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="I33" s="5" t="inlineStr">
-        <is>
-          <t>19-Aug-2026</t>
-        </is>
-      </c>
-      <c r="J33" s="5" t="inlineStr">
-        <is>
-          <t>EXPIRING SOON</t>
-        </is>
-      </c>
-      <c r="K33" s="5" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="5" t="n">
-        <v>32</v>
-      </c>
-      <c r="B34" s="5" t="inlineStr">
-        <is>
-          <t>Equipment Request &amp; Handover Procedure(AMH) (SOPs)</t>
-        </is>
-      </c>
-      <c r="C34" s="5" t="inlineStr"/>
-      <c r="D34" s="5" t="inlineStr"/>
-      <c r="E34" s="5" t="inlineStr"/>
-      <c r="F34" s="5" t="inlineStr">
-        <is>
-          <t>24-Aug-2025</t>
-        </is>
-      </c>
-      <c r="G34" s="5" t="inlineStr">
-        <is>
-          <t>24-Aug-2026</t>
-        </is>
-      </c>
-      <c r="H34" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="I34" s="5" t="inlineStr">
-        <is>
-          <t>19-Aug-2026</t>
-        </is>
-      </c>
-      <c r="J34" s="5" t="inlineStr">
-        <is>
-          <t>EXPIRING SOON</t>
-        </is>
-      </c>
-      <c r="K34" s="5" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="5" t="n">
-        <v>33</v>
-      </c>
-      <c r="B35" s="5" t="inlineStr">
-        <is>
-          <t>Storage Retrieval Machine Software Recovery Procedure (SOPs)</t>
-        </is>
-      </c>
-      <c r="C35" s="5" t="inlineStr"/>
-      <c r="D35" s="5" t="inlineStr"/>
-      <c r="E35" s="5" t="inlineStr"/>
-      <c r="F35" s="5" t="inlineStr">
+      <c r="K35" s="4" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="n">
+        <v>34</v>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>ASRS Operation Recovery Procedure (SOPs)</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr"/>
+      <c r="D36" s="4" t="inlineStr"/>
+      <c r="E36" s="4" t="inlineStr"/>
+      <c r="F36" s="4" t="inlineStr">
         <is>
           <t>25-Aug-2025</t>
         </is>
       </c>
-      <c r="G35" s="5" t="inlineStr">
+      <c r="G36" s="4" t="inlineStr">
         <is>
           <t>25-Aug-2026</t>
         </is>
       </c>
-      <c r="H35" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="I35" s="5" t="inlineStr">
-        <is>
-          <t>19-Aug-2026</t>
-        </is>
-      </c>
-      <c r="J35" s="5" t="inlineStr">
-        <is>
-          <t>EXPIRING SOON</t>
-        </is>
-      </c>
-      <c r="K35" s="5" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="5" t="n">
-        <v>34</v>
-      </c>
-      <c r="B36" s="5" t="inlineStr">
-        <is>
-          <t>ASRS Operation Recovery Procedure (SOPs)</t>
-        </is>
-      </c>
-      <c r="C36" s="5" t="inlineStr"/>
-      <c r="D36" s="5" t="inlineStr"/>
-      <c r="E36" s="5" t="inlineStr"/>
-      <c r="F36" s="5" t="inlineStr">
-        <is>
-          <t>25-Aug-2025</t>
-        </is>
-      </c>
-      <c r="G36" s="5" t="inlineStr">
-        <is>
-          <t>25-Aug-2026</t>
-        </is>
-      </c>
-      <c r="H36" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="I36" s="5" t="inlineStr">
-        <is>
-          <t>19-Aug-2026</t>
-        </is>
-      </c>
-      <c r="J36" s="5" t="inlineStr">
-        <is>
-          <t>EXPIRING SOON</t>
-        </is>
-      </c>
-      <c r="K36" s="5" t="inlineStr"/>
+      <c r="H36" s="4" t="n">
+        <v>-3</v>
+      </c>
+      <c r="I36" s="4" t="inlineStr">
+        <is>
+          <t>27-Aug-2026</t>
+        </is>
+      </c>
+      <c r="J36" s="4" t="inlineStr">
+        <is>
+          <t>EXPIRED</t>
+        </is>
+      </c>
+      <c r="K36" s="4" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="5" t="n">
+      <c r="A37" s="4" t="n">
         <v>35</v>
       </c>
-      <c r="B37" s="5" t="inlineStr">
+      <c r="B37" s="4" t="inlineStr">
         <is>
           <t>Storage Retrieval Machine Software Recovery Procedure.1 (SOPs)</t>
         </is>
       </c>
-      <c r="C37" s="5" t="inlineStr"/>
-      <c r="D37" s="5" t="inlineStr"/>
-      <c r="E37" s="5" t="inlineStr"/>
-      <c r="F37" s="5" t="inlineStr">
+      <c r="C37" s="4" t="inlineStr"/>
+      <c r="D37" s="4" t="inlineStr"/>
+      <c r="E37" s="4" t="inlineStr"/>
+      <c r="F37" s="4" t="inlineStr">
         <is>
           <t>26-Aug-2025</t>
         </is>
       </c>
-      <c r="G37" s="5" t="inlineStr">
+      <c r="G37" s="4" t="inlineStr">
         <is>
           <t>26-Aug-2026</t>
         </is>
       </c>
-      <c r="H37" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="I37" s="5" t="inlineStr">
-        <is>
-          <t>19-Aug-2026</t>
-        </is>
-      </c>
-      <c r="J37" s="5" t="inlineStr">
-        <is>
-          <t>EXPIRING SOON</t>
-        </is>
-      </c>
-      <c r="K37" s="5" t="inlineStr"/>
+      <c r="H37" s="4" t="n">
+        <v>-2</v>
+      </c>
+      <c r="I37" s="4" t="inlineStr">
+        <is>
+          <t>27-Aug-2026</t>
+        </is>
+      </c>
+      <c r="J37" s="4" t="inlineStr">
+        <is>
+          <t>EXPIRED</t>
+        </is>
+      </c>
+      <c r="K37" s="4" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="5" t="n">
+      <c r="A38" s="4" t="n">
         <v>36</v>
       </c>
-      <c r="B38" s="5" t="inlineStr">
+      <c r="B38" s="4" t="inlineStr">
         <is>
           <t>Sorting Transfer Vehicle Operation (SOPs)</t>
         </is>
       </c>
-      <c r="C38" s="5" t="inlineStr"/>
-      <c r="D38" s="5" t="inlineStr"/>
-      <c r="E38" s="5" t="inlineStr"/>
-      <c r="F38" s="5" t="inlineStr">
+      <c r="C38" s="4" t="inlineStr"/>
+      <c r="D38" s="4" t="inlineStr"/>
+      <c r="E38" s="4" t="inlineStr"/>
+      <c r="F38" s="4" t="inlineStr">
         <is>
           <t>26-Aug-2025</t>
         </is>
       </c>
-      <c r="G38" s="5" t="inlineStr">
+      <c r="G38" s="4" t="inlineStr">
         <is>
           <t>26-Aug-2026</t>
         </is>
       </c>
-      <c r="H38" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="I38" s="5" t="inlineStr">
-        <is>
-          <t>19-Aug-2026</t>
-        </is>
-      </c>
-      <c r="J38" s="5" t="inlineStr">
-        <is>
-          <t>EXPIRING SOON</t>
-        </is>
-      </c>
-      <c r="K38" s="5" t="inlineStr"/>
+      <c r="H38" s="4" t="n">
+        <v>-2</v>
+      </c>
+      <c r="I38" s="4" t="inlineStr">
+        <is>
+          <t>27-Aug-2026</t>
+        </is>
+      </c>
+      <c r="J38" s="4" t="inlineStr">
+        <is>
+          <t>EXPIRED</t>
+        </is>
+      </c>
+      <c r="K38" s="4" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="5" t="n">
+      <c r="A39" s="4" t="n">
         <v>37</v>
       </c>
-      <c r="B39" s="5" t="inlineStr">
+      <c r="B39" s="4" t="inlineStr">
         <is>
           <t>AMH FT-12 Basic Calibration Setup (SOPs)</t>
         </is>
       </c>
-      <c r="C39" s="5" t="inlineStr"/>
-      <c r="D39" s="5" t="inlineStr"/>
-      <c r="E39" s="5" t="inlineStr"/>
-      <c r="F39" s="5" t="inlineStr">
+      <c r="C39" s="4" t="inlineStr"/>
+      <c r="D39" s="4" t="inlineStr"/>
+      <c r="E39" s="4" t="inlineStr"/>
+      <c r="F39" s="4" t="inlineStr">
         <is>
           <t>27-Aug-2025</t>
         </is>
       </c>
-      <c r="G39" s="5" t="inlineStr">
-        <is>
-          <t>27-Aug-2026</t>
-        </is>
-      </c>
-      <c r="H39" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="I39" s="5" t="inlineStr">
-        <is>
-          <t>19-Aug-2026</t>
-        </is>
-      </c>
-      <c r="J39" s="5" t="inlineStr">
-        <is>
-          <t>EXPIRING SOON</t>
-        </is>
-      </c>
-      <c r="K39" s="5" t="inlineStr"/>
+      <c r="G39" s="4" t="inlineStr">
+        <is>
+          <t>27-Aug-2026</t>
+        </is>
+      </c>
+      <c r="H39" s="4" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I39" s="4" t="inlineStr">
+        <is>
+          <t>27-Aug-2026</t>
+        </is>
+      </c>
+      <c r="J39" s="4" t="inlineStr">
+        <is>
+          <t>EXPIRED</t>
+        </is>
+      </c>
+      <c r="K39" s="4" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="5" t="n">
+      <c r="A40" s="4" t="n">
         <v>38</v>
       </c>
-      <c r="B40" s="5" t="inlineStr">
+      <c r="B40" s="4" t="inlineStr">
         <is>
           <t>AMH Conveyors Operation (SOPs)</t>
         </is>
       </c>
-      <c r="C40" s="5" t="inlineStr"/>
-      <c r="D40" s="5" t="inlineStr"/>
-      <c r="E40" s="5" t="inlineStr"/>
-      <c r="F40" s="5" t="inlineStr">
+      <c r="C40" s="4" t="inlineStr"/>
+      <c r="D40" s="4" t="inlineStr"/>
+      <c r="E40" s="4" t="inlineStr"/>
+      <c r="F40" s="4" t="inlineStr">
         <is>
           <t>27-Aug-2025</t>
         </is>
       </c>
-      <c r="G40" s="5" t="inlineStr">
-        <is>
-          <t>27-Aug-2026</t>
-        </is>
-      </c>
-      <c r="H40" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="I40" s="5" t="inlineStr">
-        <is>
-          <t>19-Aug-2026</t>
-        </is>
-      </c>
-      <c r="J40" s="5" t="inlineStr">
-        <is>
-          <t>EXPIRING SOON</t>
-        </is>
-      </c>
-      <c r="K40" s="5" t="inlineStr"/>
+      <c r="G40" s="4" t="inlineStr">
+        <is>
+          <t>27-Aug-2026</t>
+        </is>
+      </c>
+      <c r="H40" s="4" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I40" s="4" t="inlineStr">
+        <is>
+          <t>27-Aug-2026</t>
+        </is>
+      </c>
+      <c r="J40" s="4" t="inlineStr">
+        <is>
+          <t>EXPIRED</t>
+        </is>
+      </c>
+      <c r="K40" s="4" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="3" t="n">
@@ -2296,11 +2287,11 @@
         </is>
       </c>
       <c r="H41" s="3" t="n">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="I41" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J41" s="3" t="inlineStr">
@@ -2309,6 +2300,43 @@
         </is>
       </c>
       <c r="K41" s="3" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>IS0 55001 (Other Trainings)</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr"/>
+      <c r="D42" s="3" t="inlineStr"/>
+      <c r="E42" s="3" t="inlineStr"/>
+      <c r="F42" s="3" t="inlineStr">
+        <is>
+          <t>24-Aug-2026</t>
+        </is>
+      </c>
+      <c r="G42" s="3" t="inlineStr">
+        <is>
+          <t>23-Aug-2028</t>
+        </is>
+      </c>
+      <c r="H42" s="3" t="n">
+        <v>726</v>
+      </c>
+      <c r="I42" s="3" t="inlineStr">
+        <is>
+          <t>27-Aug-2026</t>
+        </is>
+      </c>
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="K42" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2324,7 +2352,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -2475,47 +2503,78 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
+          <t>Logimat</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>17-Aug-2026</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>96.00%</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>Approved Score. date is valid</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
           <t>Bin Transport System</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>22-Dec-2025</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="D7" s="3" t="inlineStr">
         <is>
           <t>93.94%</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="E7" s="3" t="inlineStr">
         <is>
           <t>VALID</t>
         </is>
       </c>
-      <c r="F6" s="3" t="inlineStr">
+      <c r="F7" s="3" t="inlineStr">
         <is>
           <t>Approved Score. date is valid</t>
         </is>
       </c>
-      <c r="G6" s="3" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr"/>
-      <c r="B7" s="3" t="inlineStr"/>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="G7" s="3" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr"/>
+      <c r="B8" s="3" t="inlineStr"/>
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>TOTAL AVERAGE</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>80.38%</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr"/>
-      <c r="F7" s="3" t="inlineStr"/>
-      <c r="G7" s="3" t="n"/>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>83.50%</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr"/>
+      <c r="F8" s="3" t="inlineStr"/>
+      <c r="G8" s="3" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2603,7 +2662,7 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>7617</v>
+        <v>7609</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -2632,7 +2691,7 @@
         </is>
       </c>
       <c r="E4" s="3" t="n">
-        <v>7797</v>
+        <v>7789</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
